--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487420_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487420_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X20"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7305</v>
+        <v>4.8899</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8557</v>
+        <v>4.1754</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8749</v>
+        <v>0.7145</v>
       </c>
       <c r="G2" t="n">
         <v>5.3298</v>
@@ -610,13 +610,13 @@
         <v>1.9585</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8132</v>
+        <v>0.9725</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3596</v>
+        <v>0.6793</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4536</v>
+        <v>0.2932</v>
       </c>
       <c r="V2" t="n">
         <v>-1.2166</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1513</v>
+        <v>3.5066</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6606</v>
+        <v>0.9246</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4908</v>
+        <v>2.5819</v>
       </c>
       <c r="G3" t="n">
         <v>-1.1371</v>
@@ -688,13 +688,13 @@
         <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4796</v>
+        <v>0.8349</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3694</v>
+        <v>-0.1053</v>
       </c>
       <c r="U3" t="n">
-        <v>1.849</v>
+        <v>0.9401</v>
       </c>
       <c r="V3" t="n">
         <v>4.2005</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8088</v>
+        <v>3.0761</v>
       </c>
       <c r="E4" t="n">
         <v>3.292</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4832</v>
+        <v>-0.2158</v>
       </c>
       <c r="G4" t="n">
         <v>3.2321</v>
@@ -766,13 +766,13 @@
         <v>0.7834</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0065</v>
+        <v>0.2738</v>
       </c>
       <c r="T4" t="n">
         <v>0.207</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2005</v>
+        <v>0.0668</v>
       </c>
       <c r="V4" t="n">
         <v>0.9412</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. YUBERO ROSALES</t>
+          <t>M. OILLATAGUERRE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7371</v>
+        <v>0.9507</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9693000000000001</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7678</v>
+        <v>0.1397</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3868</v>
+        <v>0.3045</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8918</v>
+        <v>0.3954</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.495</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5806</v>
+        <v>2.0003</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.621</v>
+        <v>1.9598</v>
       </c>
       <c r="L5" t="n">
         <v>0.0404</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8062</v>
+        <v>-1.6957</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2708</v>
+        <v>-1.5645</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5354</v>
+        <v>-0.1313</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1958</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7834</v>
+        <v>1.1751</v>
       </c>
       <c r="S5" t="n">
-        <v>2.3785</v>
+        <v>0.7637</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2537</v>
+        <v>0.7693</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1247</v>
+        <v>-0.0056</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9412</v>
+        <v>0.6659</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0.6659</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. OILLATAGUERRE</t>
+          <t>D. SNYERS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4833</v>
+        <v>0.9115</v>
       </c>
       <c r="E6" t="n">
-        <v>0.504</v>
+        <v>0.3164</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0207</v>
+        <v>0.595</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3045</v>
+        <v>-2.2292</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3954</v>
+        <v>-0.1473</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-2.0819</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0003</v>
+        <v>-0.4793</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9598</v>
+        <v>1.4818</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0404</v>
+        <v>-1.9611</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6957</v>
+        <v>-1.7499</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.5645</v>
+        <v>-1.629</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1313</v>
+        <v>-0.1209</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7834</v>
+        <v>1.5668</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9585</v>
+        <v>-0.1958</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1751</v>
+        <v>1.7626</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2963</v>
+        <v>0.8504</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4623</v>
+        <v>0.9916</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.166</v>
+        <v>-0.1411</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6659</v>
+        <v>0.7235</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6659</v>
+        <v>0.7235</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. SANCHEZ VAZQUEZ</t>
+          <t>S. YUBERO ROSALES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2022</v>
+        <v>0.6532</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2955</v>
+        <v>-0.3017</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4977</v>
+        <v>0.9549</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3387</v>
+        <v>-1.3868</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.9197</v>
+        <v>-0.8918</v>
       </c>
       <c r="I7" t="n">
-        <v>0.581</v>
+        <v>-0.495</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6727</v>
+        <v>-0.5806</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5802</v>
+        <v>-0.621</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2529</v>
+        <v>0.0404</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.0114</v>
+        <v>-0.8062</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3396</v>
+        <v>-0.2708</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.5354</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5875</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5875</v>
+        <v>0.7834</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7655999999999999</v>
+        <v>1.2946</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6228</v>
+        <v>0.9828</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1427</v>
+        <v>0.3119</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2166</v>
+        <v>0.9412</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2166</v>
+        <v>0.6659</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. SNYERS</t>
+          <t>L. SANCHEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6327</v>
+        <v>0.1804</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0139</v>
+        <v>1.7049</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3812</v>
+        <v>-1.5245</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.2292</v>
+        <v>-0.3387</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1473</v>
+        <v>-0.9197</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.0819</v>
+        <v>0.581</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4793</v>
+        <v>0.6727</v>
       </c>
       <c r="K8" t="n">
-        <v>1.4818</v>
+        <v>-0.5802</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.9611</v>
+        <v>1.2529</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7499</v>
+        <v>-1.0114</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.629</v>
+        <v>-0.3396</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1209</v>
+        <v>-0.6719000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5668</v>
+        <v>0.5875</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1958</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7626</v>
+        <v>0.5875</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6938</v>
+        <v>1.1482</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3388</v>
+        <v>1.0322</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.355</v>
+        <v>0.116</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7235</v>
+        <v>-1.2166</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.7235</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. LUACES PENIN</t>
+          <t>P. ROQUE DO VALE CARVAHAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0449</v>
+        <v>-0.649</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9588</v>
+        <v>-2.1002</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0861</v>
+        <v>1.4512</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0421</v>
+        <v>3.2492</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0473</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0052</v>
+        <v>3.1624</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0204</v>
+        <v>1.3963</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0204</v>
+        <v>-0.3964</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.7927</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0625</v>
+        <v>1.8529</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0677</v>
+        <v>0.4833</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0052</v>
+        <v>1.3697</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.7834</v>
+        <v>-2.3502</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9792</v>
+        <v>-3.1336</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1958</v>
+        <v>0.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2194</v>
+        <v>-0.3314</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-0.3629</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2194</v>
+        <v>0.0315</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. ROQUE DO VALE CARVAHAL</t>
+          <t>I. LUACES PENIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1712</v>
+        <v>-0.8624000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5689</v>
+        <v>-0.8565</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3978</v>
+        <v>-0.0059</v>
       </c>
       <c r="G10" t="n">
-        <v>3.2492</v>
+        <v>-0.0421</v>
       </c>
       <c r="H10" t="n">
-        <v>0.08690000000000001</v>
+        <v>-0.0473</v>
       </c>
       <c r="I10" t="n">
-        <v>3.1624</v>
+        <v>0.0052</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3963</v>
+        <v>0.0204</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.3964</v>
+        <v>0.0204</v>
       </c>
       <c r="L10" t="n">
-        <v>1.7927</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.8529</v>
+        <v>-0.0625</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4833</v>
+        <v>-0.0677</v>
       </c>
       <c r="O10" t="n">
-        <v>1.3697</v>
+        <v>0.0052</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.3502</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1336</v>
+        <v>-0.9792</v>
       </c>
       <c r="R10" t="n">
-        <v>0.7834</v>
+        <v>0.1958</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8536</v>
+        <v>-0.0369</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8316</v>
+        <v>0.1023</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.022</v>
+        <v>-0.1392</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5253</v>
+        <v>-3.0252</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.6127</v>
+        <v>-3.2463</v>
       </c>
       <c r="F11" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.2211</v>
       </c>
       <c r="G11" t="n">
         <v>-1.5757</v>
@@ -1312,13 +1312,13 @@
         <v>1.9585</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.362</v>
+        <v>0.1381</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3694</v>
+        <v>-0.0029</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0074</v>
+        <v>0.141</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6083</v>
@@ -1345,25 +1345,25 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.334700000000002</v>
+        <v>9.6318</v>
       </c>
       <c r="E12" t="n">
-        <v>4.422799999999999</v>
+        <v>4.7196</v>
       </c>
       <c r="F12" t="n">
-        <v>4.9122</v>
+        <v>4.912100000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>5.405999999999999</v>
+        <v>5.406</v>
       </c>
       <c r="H12" t="n">
-        <v>5.457800000000001</v>
+        <v>5.4578</v>
       </c>
       <c r="I12" t="n">
         <v>-0.05180000000000051</v>
       </c>
       <c r="J12" t="n">
-        <v>9.3383</v>
+        <v>9.338300000000002</v>
       </c>
       <c r="K12" t="n">
         <v>12.223</v>
@@ -1390,22 +1390,22 @@
         <v>11.7508</v>
       </c>
       <c r="S12" t="n">
-        <v>5.610899999999999</v>
+        <v>5.9079</v>
       </c>
       <c r="T12" t="n">
-        <v>3.9962</v>
+        <v>4.293399999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6145</v>
+        <v>1.6146</v>
       </c>
       <c r="V12" t="n">
-        <v>3.214200000000002</v>
+        <v>3.214200000000001</v>
       </c>
       <c r="W12" t="n">
-        <v>7.7352</v>
+        <v>7.735200000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.5209</v>
+        <v>-4.520899999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.8113</v>
+        <v>2.9315</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7883</v>
+        <v>1.5047</v>
       </c>
       <c r="F13" t="n">
-        <v>1.023</v>
+        <v>1.4268</v>
       </c>
       <c r="G13" t="n">
         <v>2.8136</v>
@@ -1468,13 +1468,13 @@
         <v>2.7419</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.7419</v>
+        <v>-1.6218</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3662</v>
+        <v>-0.6499</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3756</v>
+        <v>-0.9719</v>
       </c>
       <c r="V13" t="n">
         <v>-0.023</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. KOUROUMA</t>
+          <t>A. SMITH</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6208</v>
+        <v>0.1099</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2129</v>
+        <v>1.7489</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5921</v>
+        <v>-1.639</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1044</v>
+        <v>-3.8903</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.1764</v>
+        <v>-1.6619</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0719</v>
+        <v>-2.2284</v>
       </c>
       <c r="J14" t="n">
-        <v>2.309</v>
+        <v>-1.6758</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5411</v>
+        <v>1.1243</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7679</v>
+        <v>-2.8001</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.4135</v>
+        <v>-2.2145</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.7175</v>
+        <v>-2.7862</v>
       </c>
       <c r="O14" t="n">
-        <v>0.304</v>
+        <v>0.5717</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7834</v>
+        <v>3.1336</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.917</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>3.1336</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1388</v>
+        <v>-0.2694</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9936</v>
+        <v>-0.4429</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1452</v>
+        <v>0.1735</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.6302</v>
+        <v>1.136</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.1728</v>
+        <v>3.8676</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.4574</v>
+        <v>-2.7316</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. CHOITHRAMANI BLANCO</t>
+          <t>A. ROA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3546</v>
+        <v>0.1023</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5962</v>
+        <v>0.1023</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9507</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.4473</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.048</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3993</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.84</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1258</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.9659</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.6072</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.1738</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5666</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.546</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.546</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5542</v>
+        <v>0.1023</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2439</v>
+        <v>0.1023</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3103</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.2984</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2984</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. SMITH</t>
+          <t>R. CHOITHRAMANI BLANCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8499</v>
+        <v>-0.7462</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0325</v>
+        <v>-1.6195</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8824</v>
+        <v>0.8733</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.8903</v>
+        <v>-3.4473</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.6619</v>
+        <v>-2.048</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.2284</v>
+        <v>-1.3993</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.6758</v>
+        <v>-1.84</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1243</v>
+        <v>0.1258</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.8001</v>
+        <v>-1.9659</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.2145</v>
+        <v>-1.6072</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.7862</v>
+        <v>-2.1738</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5717</v>
+        <v>0.5666</v>
       </c>
       <c r="P16" t="n">
-        <v>3.1336</v>
+        <v>2.546</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1336</v>
+        <v>2.546</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2291</v>
+        <v>0.4535</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1592</v>
+        <v>0.2205</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0699</v>
+        <v>0.2329</v>
       </c>
       <c r="V16" t="n">
-        <v>1.136</v>
+        <v>-0.2984</v>
       </c>
       <c r="W16" t="n">
-        <v>3.8676</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.7316</v>
+        <v>-0.2984</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. PETERS</t>
+          <t>O. KOUROUMA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.6413</v>
+        <v>-2.4205</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.1914</v>
+        <v>-1.2432</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.4499</v>
+        <v>-1.1774</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2631</v>
+        <v>-0.1044</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3083</v>
+        <v>-1.1764</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0452</v>
+        <v>1.0719</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1829</v>
+        <v>2.309</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1021</v>
+        <v>1.5411</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0808</v>
+        <v>0.7679</v>
       </c>
       <c r="M17" t="n">
-        <v>0.08019999999999999</v>
+        <v>-2.4135</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2062</v>
+        <v>-2.7175</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1261</v>
+        <v>0.304</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3709</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9585</v>
+        <v>-3.917</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5875</v>
+        <v>3.1336</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2581</v>
+        <v>0.0975</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4158</v>
+        <v>0.5375</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8423</v>
+        <v>-0.4401</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2754</v>
+        <v>-1.6302</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.1728</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2754</v>
+        <v>-1.4574</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. GARRIDO RODRIGUEZ</t>
+          <t>R. PETERS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.0761</v>
+        <v>-2.5611</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2849</v>
+        <v>-2.1914</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7911</v>
+        <v>-0.3697</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.6545</v>
+        <v>0.2631</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0837</v>
+        <v>0.3083</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.7382</v>
+        <v>-0.0452</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1559</v>
+        <v>0.1829</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5107</v>
+        <v>0.1021</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3548</v>
+        <v>0.0808</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8104</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.427</v>
+        <v>0.2062</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3834</v>
+        <v>-0.1261</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7834</v>
+        <v>-1.3709</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7626</v>
+        <v>0.5875</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.9884</v>
+        <v>-1.1779</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.1286</v>
+        <v>-0.4158</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8597</v>
+        <v>-0.7621</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2166</v>
+        <v>-0.2754</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.8837</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.5543</v>
+        <v>-2.918</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8734</v>
+        <v>-1.7477</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.6809</v>
+        <v>-1.1703</v>
       </c>
       <c r="G19" t="n">
         <v>0.6139</v>
@@ -1936,13 +1936,13 @@
         <v>2.7419</v>
       </c>
       <c r="S19" t="n">
-        <v>-3.0864</v>
+        <v>-1.4501</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.7821</v>
+        <v>-0.6564</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.3044</v>
+        <v>-0.7937</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9067</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>A. GARRIDO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,66 +1969,144 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-9.334899999999999</v>
+        <v>-3.1504</v>
       </c>
       <c r="E20" t="n">
+        <v>-1.4663</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-1.6842</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-1.6545</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.0837</v>
+      </c>
+      <c r="I20" t="n">
+        <v>-1.7382</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.1559</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1.5107</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-1.3548</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-1.8104</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-1.427</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-0.3834</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.7834</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-0.9792</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.7626</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-1.0628</v>
+      </c>
+      <c r="T20" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-0.7528</v>
+      </c>
+      <c r="V20" t="n">
+        <v>-1.2166</v>
+      </c>
+      <c r="W20" t="n">
+        <v>-0.3329</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.8837</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PERFUMERIAS AVENIDA XOBORG</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-8.6525</v>
+      </c>
+      <c r="E21" t="n">
         <v>-4.9122</v>
       </c>
-      <c r="F20" t="n">
-        <v>-4.4227</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-5.4059</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-5.457999999999999</v>
-      </c>
-      <c r="I20" t="n">
+      <c r="F21" t="n">
+        <v>-3.7405</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-5.405899999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-5.458</v>
+      </c>
+      <c r="I21" t="n">
         <v>0.05199999999999982</v>
       </c>
-      <c r="J20" t="n">
-        <v>3.932500000000001</v>
-      </c>
-      <c r="K20" t="n">
+      <c r="J21" t="n">
+        <v>3.9325</v>
+      </c>
+      <c r="K21" t="n">
         <v>6.7651</v>
       </c>
-      <c r="L20" t="n">
+      <c r="L21" t="n">
         <v>-2.8327</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M21" t="n">
         <v>-9.3384</v>
       </c>
-      <c r="N20" t="n">
+      <c r="N21" t="n">
         <v>-12.223</v>
       </c>
-      <c r="O20" t="n">
+      <c r="O21" t="n">
         <v>2.8846</v>
       </c>
-      <c r="P20" t="n">
-        <v>4.8962</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="P21" t="n">
+        <v>4.896199999999999</v>
+      </c>
+      <c r="Q21" t="n">
         <v>-11.7509</v>
       </c>
-      <c r="R20" t="n">
+      <c r="R21" t="n">
         <v>16.6471</v>
       </c>
-      <c r="S20" t="n">
-        <v>-5.610899999999999</v>
-      </c>
-      <c r="T20" t="n">
-        <v>-1.6144</v>
-      </c>
-      <c r="U20" t="n">
-        <v>-3.9964</v>
-      </c>
-      <c r="V20" t="n">
+      <c r="S21" t="n">
+        <v>-4.9287</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-1.6147</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-3.3142</v>
+      </c>
+      <c r="V21" t="n">
         <v>-3.2143</v>
       </c>
-      <c r="W20" t="n">
+      <c r="W21" t="n">
         <v>4.521</v>
       </c>
-      <c r="X20" t="n">
+      <c r="X21" t="n">
         <v>-7.735300000000001</v>
       </c>
     </row>
